--- a/docs/testing/danh-muc-test/backend-inventory-service.xlsx
+++ b/docs/testing/danh-muc-test/backend-inventory-service.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Danh mục test" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Danh mục test'!$A$5:$H$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Danh mục test'!$A$5:$H$256</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA(A6:A255)</f>
+        <f>COUNTA(A6:A256)</f>
         <v/>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -539,11 +539,11 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIF(G6:G255,"Đạt")</f>
+        <f>COUNTIF(G6:G256,"Đạt")</f>
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>"Đỏ: "&amp;COUNTIF(G6:G255,"Đỏ")&amp;"   ·   Bỏ qua: "&amp;COUNTIF(G6:G255,"Bỏ qua")</f>
+        <f>"Đỏ: "&amp;COUNTIF(G6:G256,"Đỏ")&amp;"   ·   Bỏ qua: "&amp;COUNTIF(G6:G256,"Bỏ qua")</f>
         <v/>
       </c>
     </row>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.114</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="7">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.216</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="8">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="9">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.05</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="11">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="12">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="14">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="15">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="16">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.023</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="17">
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="19">
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="20">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="22">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="23">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="25">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="26">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="27">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="28">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="29">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="30">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="32">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="34">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="36">
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="38">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="39">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.03</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="40">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="42">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="43">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="44">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="45">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="46">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="47">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.014</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="48">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="49">
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.006</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="50">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="52">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="53">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="54">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="55">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.004</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="56">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="57">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="58">
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="59">
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="60">
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="61">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="62">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="63">
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="66">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.005</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="70">
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="71">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="73">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="74">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.013</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="75">
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="77">
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="78">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>3.635</v>
+        <v>4.671</v>
       </c>
     </row>
     <row r="79">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>0.488</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="80">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>0.026</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="81">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="H82" s="5" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="83">
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="84">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="85">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="86">
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="H86" s="5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="87">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="88">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="89">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="90">
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="H90" s="5" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="91">
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="92">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="93">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="94">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="95">
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="97">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="98">
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="99">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="100">
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="H100" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="101">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="102">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="105">
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="107">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="109">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="110">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="112">
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="113">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="116">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="117">
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="119">
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="121">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="124">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="H126" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="127">
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="H127" s="5" t="n">
-        <v>0.114</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="128">
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="H128" s="5" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="129">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="H129" s="5" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="130">
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="H130" s="5" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="131">
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="H131" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="132">
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c r="H132" s="5" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="133">
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="H133" s="5" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="134">
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="135">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H135" s="5" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="136">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="H136" s="5" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="137">
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="H138" s="5" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="139">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="H139" s="5" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="140">
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="H140" s="5" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="141">
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="H141" s="5" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="142">
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="H142" s="5" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="143">
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="144">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="H144" s="5" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="145">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="H146" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="147">
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="H147" s="5" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="148">
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="H148" s="5" t="n">
-        <v>0.042</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="149">
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="H149" s="5" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="150">
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="151">
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="H151" s="5" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="152">
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="H154" s="5" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="155">
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="H155" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="156">
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="H156" s="5" t="n">
-        <v>0.029</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="157">
@@ -6262,7 +6262,7 @@
         </is>
       </c>
       <c r="H157" s="5" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="158">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="H158" s="5" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="159">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="H160" s="5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="161">
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="H161" s="5" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="H162" s="5" t="n">
-        <v>0.352</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="163">
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="H163" s="5" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="164">
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="H164" s="5" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="165">
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="H165" s="5" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="166">
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="H166" s="5" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="167">
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="H167" s="5" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="168">
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="H168" s="5" t="n">
-        <v>0.003</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="169">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="H169" s="5" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="170">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="H170" s="5" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="171">
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="H171" s="5" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="172">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="174">
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="H174" s="5" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="175">
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="H176" s="5" t="n">
-        <v>0.154</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="177">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="178">
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="179">
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="180">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="H180" s="5" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="181">
@@ -7166,7 +7166,7 @@
         </is>
       </c>
       <c r="H181" s="5" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="182">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="H182" s="5" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="183">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="H184" s="5" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="185">
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="H185" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="186">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="187">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="H187" s="5" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="188">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>0.028</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="189">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="H189" s="5" t="n">
-        <v>0.019</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="190">
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>0.021</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="192">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="193">
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="H194" s="5" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="195">
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="H195" s="5" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="196">
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="197">
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="H197" s="5" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="198">
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="199">
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="200">
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="202">
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="H202" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="203">
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="H203" s="5" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="204">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="H204" s="5" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="H205" s="5" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="206">
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="207">
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="H207" s="5" t="n">
-        <v>0.041</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="208">
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="H208" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="209">
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="H209" s="5" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="210">
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="211">
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="H211" s="5" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="212">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="H212" s="5" t="n">
-        <v>1.734</v>
+        <v>1.744</v>
       </c>
     </row>
     <row r="213">
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="H213" s="5" t="n">
-        <v>0.126</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="214">
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="H214" s="5" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="215">
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="H215" s="5" t="n">
-        <v>0.091</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="216">
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="H216" s="5" t="n">
-        <v>0.12</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="217">
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="H217" s="5" t="n">
-        <v>0.078</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="218">
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="H218" s="5" t="n">
-        <v>0.076</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="219">
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="H219" s="5" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="220">
@@ -8600,7 +8600,7 @@
         </is>
       </c>
       <c r="H220" s="5" t="n">
-        <v>0.848</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="221">
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="H221" s="5" t="n">
-        <v>0.032</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="222">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H222" s="5" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="223">
@@ -8688,12 +8688,12 @@
       <c r="D223" s="6" t="inlineStr"/>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Trần mua vé từ message được áp cho đường giữ chỗ</t>
+          <t>Publish lại sau khi sửa giá: chỗ CHƯA bán lấy giá mới, chỗ đã bán / đang giữ giữ giá khách đã thấy</t>
         </is>
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>tran_mua_ve_tu_message_duoc_ap</t>
+          <t>publish_lai_thi_dong_bo_gia_cho_chua_ban</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="H223" s="5" t="n">
-        <v>0.029</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="224">
@@ -8722,12 +8722,12 @@
       <c r="D224" s="6" t="inlineStr"/>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Publish lại sau khi sửa cửa bán: chỗ giữ nguyên, nhưng cấu hình được đồng bộ</t>
+          <t>Trần mua vé từ message được áp cho đường giữ chỗ</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>publish_lai_thi_dong_bo_cua_ban</t>
+          <t>tran_mua_ve_tu_message_duoc_ap</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -8756,12 +8756,12 @@
       <c r="D225" s="6" t="inlineStr"/>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Materialize lại một suất đã có tồn kho: bỏ qua, không dựng đè</t>
+          <t>Publish lại sau khi sửa cửa bán: chỗ giữ nguyên, nhưng cấu hình được đồng bộ</t>
         </is>
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>materialize_lai_thi_bo_qua</t>
+          <t>publish_lai_thi_dong_bo_cua_ban</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="H225" s="5" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="226">
@@ -8790,12 +8790,12 @@
       <c r="D226" s="6" t="inlineStr"/>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Tồn kho vừa dựng dùng được ngay cho đường giữ chỗ</t>
+          <t>Materialize lại một suất đã có tồn kho: bỏ qua, không dựng đè</t>
         </is>
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>ton_kho_dung_duoc_ngay</t>
+          <t>materialize_lai_thi_bo_qua</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="H226" s="5" t="n">
-        <v>0.04</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="227">
@@ -8818,18 +8818,18 @@
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>OversellBackstopIT</t>
+          <t>MaterializeSessionIT</t>
         </is>
       </c>
       <c r="D227" s="6" t="inlineStr"/>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>Cổng Redis mù, 200 người giành 1 ghế: database vẫn chỉ cho đúng 1 người</t>
+          <t>Tồn kho vừa dựng dùng được ngay cho đường giữ chỗ</t>
         </is>
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>database_van_chan_khi_cong_redis_mu</t>
+          <t>ton_kho_dung_duoc_ngay</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="H227" s="5" t="n">
-        <v>0.257</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="228">
@@ -8858,12 +8858,12 @@
       <c r="D228" s="6" t="inlineStr"/>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Ghi thẳng SQL hai dòng ACTIVE cho cùng một chỗ: unique index từ chối</t>
+          <t>Cổng Redis mù, 200 người giành 1 ghế: database vẫn chỉ cho đúng 1 người</t>
         </is>
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>unique_index_tu_choi_hai_dong_active_cung_mot_cho</t>
+          <t>database_van_chan_khi_cong_redis_mu</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="H228" s="5" t="n">
-        <v>0.051</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="229">
@@ -8886,18 +8886,18 @@
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>ReleaseReserveRaceIT</t>
+          <t>OversellBackstopIT</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr"/>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>Bỏ giữ chỗ xếp hàng sau lệnh đặt chỗ đang chạy: ghế của đơn đã đặt KHÔNG được về AVAILABLE</t>
+          <t>Ghi thẳng SQL hai dòng ACTIVE cho cùng một chỗ: unique index từ chối</t>
         </is>
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>bo_giu_cho_xep_hang_sau_dat_cho</t>
+          <t>unique_index_tu_choi_hai_dong_active_cung_mot_cho</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="H229" s="5" t="n">
-        <v>0.104</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="230">
@@ -8920,18 +8920,18 @@
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
-          <t>SeatedZoneHoldIT</t>
+          <t>ReleaseReserveRaceIT</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr"/>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>xin 2 vé khu A: nhận đúng 2 ghế, và là hai ghế gần sân khấu nhất</t>
+          <t>Bỏ giữ chỗ xếp hàng sau lệnh đặt chỗ đang chạy: ghế của đơn đã đặt KHÔNG được về AVAILABLE</t>
         </is>
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>chon_cho_gan_san_khau_truoc</t>
+          <t>bo_giu_cho_xep_hang_sau_dat_cho</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="H230" s="5" t="n">
-        <v>0.064</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="231">
@@ -8960,12 +8960,12 @@
       <c r="D231" s="6" t="inlineStr"/>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>khu không còn đủ chỗ: ZONE_SOLD_OUT, và những ghế vừa cấp được nhả</t>
+          <t>xin 2 vé khu A: nhận đúng 2 ghế, và là hai ghế gần sân khấu nhất</t>
         </is>
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>khu_khong_du_cho</t>
+          <t>chon_cho_gan_san_khau_truoc</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="H231" s="5" t="n">
-        <v>0.031</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="232">
@@ -8994,12 +8994,12 @@
       <c r="D232" s="6" t="inlineStr"/>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>100 người cùng xin 2 vé ở khu 60 chỗ: phát đúng 30 lần, không ai trùng ghế</t>
+          <t>khu không còn đủ chỗ: ZONE_SOLD_OUT, và những ghế vừa cấp được nhả</t>
         </is>
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>mot_tram_nguoi_cung_xin_mot_khu</t>
+          <t>khu_khong_du_cho</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="H232" s="5" t="n">
-        <v>0.34</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="233">
@@ -9028,12 +9028,12 @@
       <c r="D233" s="6" t="inlineStr"/>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>trộn ghế đích danh với vé theo khu: cả hai vào cùng một lần giữ chỗ</t>
+          <t>100 người cùng xin 2 vé ở khu 60 chỗ: phát đúng 30 lần, không ai trùng ghế</t>
         </is>
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>tron_ghe_dich_danh_va_ve_theo_khu</t>
+          <t>mot_tram_nguoi_cung_xin_mot_khu</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -9042,7 +9042,7 @@
         </is>
       </c>
       <c r="H233" s="5" t="n">
-        <v>0.064</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="234">
@@ -9062,12 +9062,12 @@
       <c r="D234" s="6" t="inlineStr"/>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>vé theo khu đếm vào trần vé ngồi mỗi lần giữ chỗ</t>
+          <t>trộn ghế đích danh với vé theo khu: cả hai vào cùng một lần giữ chỗ</t>
         </is>
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>dem_vao_tran_ve_ngoi</t>
+          <t>tron_ghe_dich_danh_va_ve_theo_khu</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="H234" s="5" t="n">
-        <v>0.028</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="235">
@@ -9096,12 +9096,12 @@
       <c r="D235" s="6" t="inlineStr"/>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>hàng đầu đã có người: lượt sau nhận hàng kế tiếp, không nhận lại chỗ đã giữ</t>
+          <t>vé theo khu đếm vào trần vé ngồi mỗi lần giữ chỗ</t>
         </is>
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>khong_cap_lai_cho_da_giu</t>
+          <t>dem_vao_tran_ve_ngoi</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="H235" s="5" t="n">
-        <v>0.076</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="236">
@@ -9124,18 +9124,18 @@
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>SeatHoldConcurrencyIT</t>
+          <t>SeatedZoneHoldIT</t>
         </is>
       </c>
       <c r="D236" s="6" t="inlineStr"/>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Giữ chỗ hỗn hợp 2 ngồi + 2 đứng: hỏng phần đứng thì rollback cả bốn</t>
+          <t>hàng đầu đã có người: lượt sau nhận hàng kế tiếp, không nhận lại chỗ đã giữ</t>
         </is>
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>giu_cho_hon_hop_hong_mot_phan_thi_rollback_ca_bon</t>
+          <t>khong_cap_lai_cho_da_giu</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="H236" s="5" t="n">
-        <v>0.041</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="237">
@@ -9164,12 +9164,12 @@
       <c r="D237" s="6" t="inlineStr"/>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>500 người mua vé đứng ở zone 200 chỗ: phát đúng 200, không hơn một vé</t>
+          <t>Giữ chỗ hỗn hợp 2 ngồi + 2 đứng: hỏng phần đứng thì rollback cả bốn</t>
         </is>
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>nam_tram_nguoi_mua_ve_dung_zone_hai_tram</t>
+          <t>giu_cho_hon_hop_hong_mot_phan_thi_rollback_ca_bon</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="H237" s="5" t="n">
-        <v>1.803</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="238">
@@ -9198,12 +9198,12 @@
       <c r="D238" s="6" t="inlineStr"/>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Gửi trùng cùng một ghế hai lần trong một request: tính là một, không báo ghế bận</t>
+          <t>500 người mua vé đứng ở zone 200 chỗ: phát đúng 200, không hơn một vé</t>
         </is>
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>ghe_trung_lap_trong_mot_request</t>
+          <t>nam_tram_nguoi_mua_ve_dung_zone_hai_tram</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="H238" s="5" t="n">
-        <v>0.055</v>
+        <v>1.747</v>
       </c>
     </row>
     <row r="239">
@@ -9232,12 +9232,12 @@
       <c r="D239" s="6" t="inlineStr"/>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Cùng một người mở 20 tab, trần 10 vé: giữ được đúng 10 chỗ</t>
+          <t>Gửi trùng cùng một ghế hai lần trong một request: tính là một, không báo ghế bận</t>
         </is>
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>mot_nguoi_hai_muoi_tab_khong_vuot_tran_cong_don</t>
+          <t>ghe_trung_lap_trong_mot_request</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="H239" s="5" t="n">
-        <v>0.228</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="240">
@@ -9266,12 +9266,12 @@
       <c r="D240" s="6" t="inlineStr"/>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>200 người giành cùng 1 ghế: đúng 1 người giữ được</t>
+          <t>Cùng một người mở 20 tab, trần 10 vé: giữ được đúng 10 chỗ</t>
         </is>
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>hai_tram_nguoi_gianh_mot_ghe</t>
+          <t>mot_nguoi_hai_muoi_tab_khong_vuot_tran_cong_don</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="H240" s="5" t="n">
-        <v>0.252</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="241">
@@ -9294,18 +9294,18 @@
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>SeatMapIT</t>
+          <t>SeatHoldConcurrencyIT</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr"/>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>Đường đọc không làm nhảy version — nếu không, ETag đổi mỗi lần gọi và mất sạch 304</t>
+          <t>200 người giành cùng 1 ghế: đúng 1 người giữ được</t>
         </is>
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>duong_doc_khong_bump_version</t>
+          <t>hai_tram_nguoi_gianh_mot_ghe</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -9314,7 +9314,7 @@
         </is>
       </c>
       <c r="H241" s="5" t="n">
-        <v>0.067</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="242">
@@ -9334,12 +9334,12 @@
       <c r="D242" s="6" t="inlineStr"/>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Sự kiện 3.000 vé đứng KHÔNG trả 3.000 phần tử, chỉ một dòng tóm tắt mỗi zone</t>
+          <t>Đường đọc không làm nhảy version — nếu không, ETag đổi mỗi lần gọi và mất sạch 304</t>
         </is>
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>ve_dung_khong_tra_tung_don_vi</t>
+          <t>duong_doc_khong_bump_version</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="H242" s="5" t="n">
-        <v>0.767</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="243">
@@ -9368,12 +9368,12 @@
       <c r="D243" s="6" t="inlineStr"/>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Khách chưa đăng nhập vẫn xem được sơ đồ, nhưng không có phần hạn mức</t>
+          <t>Sự kiện 3.000 vé đứng KHÔNG trả 3.000 phần tử, chỉ một dòng tóm tắt mỗi zone</t>
         </is>
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>khach_an_danh_khong_co_han_muc</t>
+          <t>ve_dung_khong_tra_tung_don_vi</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -9382,7 +9382,7 @@
         </is>
       </c>
       <c r="H243" s="5" t="n">
-        <v>0.028</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="244">
@@ -9402,12 +9402,12 @@
       <c r="D244" s="6" t="inlineStr"/>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>purchaseAllowance khớp số đếm thật sau mỗi thao tác</t>
+          <t>Khách chưa đăng nhập vẫn xem được sơ đồ, nhưng không có phần hạn mức</t>
         </is>
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>han_muc_khop_so_dem_that</t>
+          <t>khach_an_danh_khong_co_han_muc</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="H244" s="5" t="n">
-        <v>0.094</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="245">
@@ -9430,18 +9430,18 @@
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>SeatReleaseIT</t>
+          <t>SeatMapIT</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr"/>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>Xác nhận thanh toán hai lần: chỉ bán một lần</t>
+          <t>purchaseAllowance khớp số đếm thật sau mỗi thao tác</t>
         </is>
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>settle_idempotent</t>
+          <t>han_muc_khop_so_dem_that</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="H245" s="5" t="n">
-        <v>0.074</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="246">
@@ -9470,12 +9470,12 @@
       <c r="D246" s="6" t="inlineStr"/>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Đường 4 — hoàn tiền CHƯA CÓ: cancel() không đụng được chỗ đã SOLD</t>
+          <t>Xác nhận thanh toán hai lần: chỉ bán một lần</t>
         </is>
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>duong_4_hoan_tien_chua_duoc_ho_tro</t>
+          <t>settle_idempotent</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="H246" s="5" t="n">
-        <v>0.077</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="247">
@@ -9504,12 +9504,12 @@
       <c r="D247" s="6" t="inlineStr"/>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>Đặt chỗ hai lần cùng orderId: idempotent, không nổ và không đổi trạng thái</t>
+          <t>Đường 4 — hoàn tiền CHƯA CÓ: cancel() không đụng được chỗ đã SOLD</t>
         </is>
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>dat_cho_idempotent_theo_order</t>
+          <t>duong_4_hoan_tien_chua_duoc_ho_tro</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -9518,7 +9518,7 @@
         </is>
       </c>
       <c r="H247" s="5" t="n">
-        <v>0.06</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="248">
@@ -9538,12 +9538,12 @@
       <c r="D248" s="6" t="inlineStr"/>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Đường 3 — huỷ đơn (saga bù trừ): chỗ đã RESERVED quay về AVAILABLE</t>
+          <t>Đặt chỗ hai lần cùng orderId: idempotent, không nổ và không đổi trạng thái</t>
         </is>
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>duong_3_huy_don</t>
+          <t>dat_cho_idempotent_theo_order</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="H248" s="5" t="n">
-        <v>0.091</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="249">
@@ -9572,12 +9572,12 @@
       <c r="D249" s="6" t="inlineStr"/>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 — giữ chỗ hết hạn: worker nhả chỗ</t>
+          <t>Đường 3 — huỷ đơn (saga bù trừ): chỗ đã RESERVED quay về AVAILABLE</t>
         </is>
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>duong_2_giu_cho_het_han</t>
+          <t>duong_3_huy_don</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="H249" s="5" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="250">
@@ -9606,12 +9606,12 @@
       <c r="D250" s="6" t="inlineStr"/>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Đường 1 — khách tự bỏ giữ chỗ: chỗ về AVAILABLE, hạn mức trả lại</t>
+          <t>Đường 2 — giữ chỗ hết hạn: worker nhả chỗ</t>
         </is>
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>duong_1_khach_tu_bo_giu_cho</t>
+          <t>duong_2_giu_cho_het_han</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="H250" s="5" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="251">
@@ -9640,12 +9640,12 @@
       <c r="D251" s="6" t="inlineStr"/>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>Không có đặt chỗ nào: bù trừ trả false chứ không ném</t>
+          <t>Đường 1 — khách tự bỏ giữ chỗ: chỗ về AVAILABLE, hạn mức trả lại</t>
         </is>
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>bu_tru_don_khong_co_dat_cho</t>
+          <t>duong_1_khach_tu_bo_giu_cho</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="H251" s="5" t="n">
-        <v>0.024</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="252">
@@ -9668,18 +9668,18 @@
       </c>
       <c r="C252" s="6" t="inlineStr">
         <is>
-          <t>SeatStatusIT</t>
+          <t>SeatReleaseIT</t>
         </is>
       </c>
       <c r="D252" s="6" t="inlineStr"/>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>chỗ bị chặn đếm riêng, không lẫn vào phần bán được</t>
+          <t>Không có đặt chỗ nào: bù trừ trả false chứ không ném</t>
         </is>
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>cho_bi_chan_dem_rieng</t>
+          <t>bu_tru_don_khong_co_dat_cho</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -9688,7 +9688,7 @@
         </is>
       </c>
       <c r="H252" s="5" t="n">
-        <v>0.033</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="253">
@@ -9708,12 +9708,12 @@
       <c r="D253" s="6" t="inlineStr"/>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>giữ chỗ chuyển AVAILABLE sang HELD trong đúng khu đó</t>
+          <t>chỗ bị chặn đếm riêng, không lẫn vào phần bán được</t>
         </is>
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>giu_cho_doi_trang_thai</t>
+          <t>cho_bi_chan_dem_rieng</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="H253" s="5" t="n">
-        <v>0.049</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="254">
@@ -9742,12 +9742,12 @@
       <c r="D254" s="6" t="inlineStr"/>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>suất chưa được dựng tồn kho: SESSION_NOT_FOUND, không phải một bảng số 0</t>
+          <t>giữ chỗ chuyển AVAILABLE sang HELD trong đúng khu đó</t>
         </is>
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>suat_chua_materialize</t>
+          <t>giu_cho_doi_trang_thai</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="H254" s="5" t="n">
-        <v>0.022</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="255">
@@ -9776,26 +9776,60 @@
       <c r="D255" s="6" t="inlineStr"/>
       <c r="E255" s="6" t="inlineStr">
         <is>
+          <t>suất chưa được dựng tồn kho: SESSION_NOT_FOUND, không phải một bảng số 0</t>
+        </is>
+      </c>
+      <c r="F255" s="6" t="inlineStr">
+        <is>
+          <t>suat_chua_materialize</t>
+        </is>
+      </c>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="n">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n">
+        <v>251</v>
+      </c>
+      <c r="B256" s="5" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="C256" s="6" t="inlineStr">
+        <is>
+          <t>SeatStatusIT</t>
+        </is>
+      </c>
+      <c r="D256" s="6" t="inlineStr"/>
+      <c r="E256" s="6" t="inlineStr">
+        <is>
           <t>gộp theo khu, và vé đứng nằm trong tổng</t>
         </is>
       </c>
-      <c r="F255" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <t>gop_theo_khu_va_gom_ca_ve_dung</t>
         </is>
       </c>
-      <c r="G255" s="5" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-      <c r="H255" s="5" t="n">
-        <v>0.073</v>
+      <c r="G256" s="5" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="H256" s="5" t="n">
+        <v>0.065</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H255"/>
-  <conditionalFormatting sqref="G6:G255">
+  <autoFilter ref="A5:H256"/>
+  <conditionalFormatting sqref="G6:G256">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Đạt"</formula>
     </cfRule>
